--- a/AI_AuditLog_Example.xlsx
+++ b/AI_AuditLog_Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kì 5\SWR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kì 5\SWR\ai-audit-log-pdung4367\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5E5D5A-1664-430C-BF13-B2872BD40C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1C09C7-0A8B-480B-AAA2-2CCBFA67D162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="155">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -60,15 +60,9 @@
     <t>Total Prompts Used (all AI tools):</t>
   </si>
   <si>
-    <t>[e.g., ~150]</t>
-  </si>
-  <si>
     <t>Core Prompts Logged:</t>
   </si>
   <si>
-    <t>[e.g., 18]</t>
-  </si>
-  <si>
     <t>Selection Ratio:</t>
   </si>
   <si>
@@ -78,9 +72,6 @@
     <t>Hallucination Detected:</t>
   </si>
   <si>
-    <t>[Count]</t>
-  </si>
-  <si>
     <t>AI TOOLS USED</t>
   </si>
   <si>
@@ -177,75 +168,18 @@
     <t>DECISION</t>
   </si>
   <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
-Contextualization: Project scope nhỏ, chỉ cần core functions.
-Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
-Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
-  </si>
-  <si>
-    <t>Screenshot comparison 10 vs 5</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
     <t>PROBLEM-SOLVING</t>
   </si>
   <si>
-    <t>Search by name quá chậm với 10K records</t>
-  </si>
-  <si>
-    <t>How to optimize search for player name in 10,000 records?</t>
-  </si>
-  <si>
-    <t>AI suggested Binary Search with O(log n) complexity</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
-Contextualization: Requirements yêu cầu partial name search.
-Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
-Decision: Chọn HashMap trade-off memory cho speed.</t>
-  </si>
-  <si>
-    <t>Code snippet + timing comparison</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
     <t>VERIFICATION</t>
   </si>
   <si>
-    <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Cần verify paper AI cite</t>
-  </si>
-  <si>
-    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
-  </si>
-  <si>
-    <t>AI confirmed it exists and provided summary</t>
-  </si>
-  <si>
-    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
-Contextualization: AI fabricated paper to answer my question.
-Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
-Decision: Replace with verified paper from Google Scholar.</t>
-  </si>
-  <si>
-    <t>Google Scholar screenshot</t>
-  </si>
-  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -273,18 +207,6 @@
     <t>Fabrication</t>
   </si>
   <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
-  </si>
-  <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
   </si>
   <si>
@@ -475,6 +397,108 @@
   </si>
   <si>
     <t>Better visual design</t>
+  </si>
+  <si>
+    <t>Use Case Analysis</t>
+  </si>
+  <si>
+    <t>Cần xác định actor và use case cho Fitness Class Booking System</t>
+  </si>
+  <si>
+    <t>Analyze Fitness Class Booking System and identify actors and use cases</t>
+  </si>
+  <si>
+    <t>AI identified Customer, Trainer, Gym Manager, Payment Gateway, Notification Service and related use cases</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đề xuất nhiều use case nhưng chưa phân biệt actor chính và actor phụ. Contextualization: Đề yêu cầu bám sát nghiệp vụ phòng gym. Creative Synthesis: Tôi giữ Customer, Trainer, Manager là actor chính; Payment Gateway và Notification Service là actor ngoài hệ thống. Decision: Điều chỉnh Use Case Diagram theo yêu cầu đề.</t>
+  </si>
+  <si>
+    <t>Use Case Diagram v1 và v2</t>
+  </si>
+  <si>
+    <t>Final Use Case Diagram</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Không phải mọi quan hệ đều cần include/extend. Contextualization: Đề yêu cầu thể hiện quan hệ UML hợp lý. Creative Synthesis: Chọn Process Payment &lt;&lt;include&gt;&gt; Create Booking, Refund &lt;&lt;extend&gt;&gt; Cancel Booking, Google Login specialization của Login. Decision: Sử dụng các quan hệ này trong sơ đồ cuối cùng.</t>
+  </si>
+  <si>
+    <t>AI suggested Payment included in Booking, Refund extends Cancel Booking, Assign Trainer extends Booking</t>
+  </si>
+  <si>
+    <t>Which use cases should use include and extend in Fitness Class Booking System?</t>
+  </si>
+  <si>
+    <t>Cần xác định include, extend, generalization trong Use Case Diagram</t>
+  </si>
+  <si>
+    <t>Use Case Relationship</t>
+  </si>
+  <si>
+    <t>Swimlane Design</t>
+  </si>
+  <si>
+    <t>Create swimlane activities for Fitness Class Booking System</t>
+  </si>
+  <si>
+    <t>AI đề xuất luồng từ Login → Browse Class → Payment → Confirmation → Feedback</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Cần đối chiếu với đề bài để tránh thêm bước không có trong requirement. Contextualization: Đề chỉ yêu cầu các hoạt động chính. Creative Synthesis: Loại bỏ bước dư thừa, giữ các bước đúng đề. Decision: Hoàn thiện Swimlane Diagram chính thức.</t>
+  </si>
+  <si>
+    <t>Chưa xác định luồng nghiệp vụ giữa Customer, System, Trainer, Manager</t>
+  </si>
+  <si>
+    <t>Swimlane Diagram</t>
+  </si>
+  <si>
+    <t>State Diagram</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Kiểm tra lại với đề để xác nhận trạng thái Waitlisted và Promoted. Contextualization: Waitlist là yêu cầu quan trọng. Creative Synthesis: Thêm Draft → Waitlisted → Promoted → Confirmed. Decision: Cập nhật State Diagram cuối cùng.</t>
+  </si>
+  <si>
+    <t>AI proposed Draft → Paid → Confirmed → Attended → Feedback Provided and cancellation paths</t>
+  </si>
+  <si>
+    <t>Verify state transitions for Fitness Class Booking System</t>
+  </si>
+  <si>
+    <t>Cần kiểm tra vòng đời Class Booking</t>
+  </si>
+  <si>
+    <t>Requirement Review</t>
+  </si>
+  <si>
+    <t>Cần xác nhận Payment Gateway và Notification Service có phải actor không</t>
+  </si>
+  <si>
+    <t>Should Payment Gateway and Notification Service be actors in Use Case Diagram?</t>
+  </si>
+  <si>
+    <t>AI explained both are external systems interacting with the booking system</t>
+  </si>
+  <si>
+    <t>Critical Thinking: So sánh với UML actor definition. Contextualization: Đây là hệ thống bên ngoài. Creative Synthesis: Giữ hai thành phần này là secondary actors. Decision: Đưa vào sơ đồ với vai trò actor ngoài hệ thống.</t>
+  </si>
+  <si>
+    <t>Revised Diagram</t>
+  </si>
+  <si>
+    <t>Over-Generalization</t>
+  </si>
+  <si>
+    <t>AI đề xuất nhiều quan hệ include/extend cho hầu hết use case</t>
+  </si>
+  <si>
+    <t>UML không yêu cầu lạm dụng include/extend</t>
+  </si>
+  <si>
+    <t>Đối chiếu tài liệu UML và yêu cầu đề bài</t>
+  </si>
+  <si>
+    <t>Chỉ giữ các quan hệ thực sự cần thiết</t>
   </si>
 </sst>
 </file>
@@ -614,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -666,6 +690,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -999,7 +1029,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1007,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -1015,7 +1045,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -1032,171 +1062,161 @@
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>10</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="4" t="e">
-        <f>C11/C10</f>
-        <v>#VALUE!</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C12" s="4"/>
       <c r="E12" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1243,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1235,7 +1255,7 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1247,127 +1267,159 @@
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
@@ -1570,7 +1622,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="22" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1580,7 +1632,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="21" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1590,47 +1642,47 @@
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
-        <v>59</v>
+      <c r="A4" s="7">
+        <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1792,73 +1844,73 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="10" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1883,7 +1935,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="18" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1891,7 +1943,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="23" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1899,204 +1951,204 @@
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="12" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A20" s="14" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="15" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="16" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A27" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2104,7 +2156,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2112,7 +2164,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
